--- a/public/static/成品导入模板.xlsx
+++ b/public/static/成品导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="成品导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>序号</t>
   </si>
@@ -316,13 +316,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
       <t>保持架</t>
     </r>
     <r>
@@ -349,6 +342,51 @@
     <t>孔径</t>
   </si>
   <si>
+    <r>
+      <t>是否销售</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>是否贸易件</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>是否生成BOM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -358,7 +396,7 @@
     <t>乘</t>
   </si>
   <si>
-    <t>自制</t>
+    <t>组装</t>
   </si>
   <si>
     <t>产品编码：需根据编码规则设置中，如果是自动生成，则无需填写，如果是手动输入，则必须输入</t>
@@ -380,6 +418,9 @@
   </si>
   <si>
     <t>导入系统中的产品，默认都是启用状态，创建时间默认当前时间，创建人默认当前导入人。</t>
+  </si>
+  <si>
+    <t>如果是贸易件时，密封盖-结构、密封盖-打字、结构类型、游隙、钢球厂家、油脂、油脂量、噪音、保持架、振动等级、精度等级、颜色、孔径等都非必填，然后产品来源固定死采购</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1424,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="CCE8CF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1633,7 +1674,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:AB48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
@@ -1649,10 +1690,13 @@
     <col min="13" max="13" width="14.6666666666667" customWidth="1"/>
     <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
     <col min="15" max="24" width="14.6666666666667" customWidth="1"/>
-    <col min="25" max="25" width="19.4444444444444" customWidth="1"/>
+    <col min="25" max="25" width="16.8888888888889" customWidth="1"/>
+    <col min="26" max="26" width="19.4444444444444" customWidth="1"/>
+    <col min="27" max="27" width="21.5555555555556" customWidth="1"/>
+    <col min="28" max="28" width="19.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:25">
+    <row r="1" ht="25" customHeight="1" spans="1:28">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1725,13 +1769,22 @@
       <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:25">
+    <row r="2" ht="20" customHeight="1" spans="1:28">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1740,10 +1793,10 @@
       <c r="F2" s="5"/>
       <c r="G2" s="4"/>
       <c r="H2" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -1760,7 +1813,10 @@
       <c r="V2" s="7"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
-      <c r="Y2" s="4"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1809,12 +1865,15 @@
     <row r="47" ht="20" customHeight="1"/>
     <row r="48" ht="20" customHeight="1"/>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"乘,除"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
-      <formula1>"自制,采购,外协"</formula1>
+      <formula1>"组装,生产,采购,外协"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 Z2 AA2">
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1833,40 +1892,44 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1"/>
+    <row r="8" ht="43" customHeight="1" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="9" ht="28" customHeight="1"/>
     <row r="10" ht="28" customHeight="1"/>
     <row r="11" ht="28" customHeight="1"/>

--- a/public/static/成品导入模板.xlsx
+++ b/public/static/成品导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="成品导入模板" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,24 @@
   </si>
   <si>
     <r>
+      <t>品名规格</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <r>
       <rPr>
         <b/>
         <sz val="12"/>
@@ -44,7 +62,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>规格型号</t>
+      <t>主单位</t>
     </r>
     <r>
       <rPr>
@@ -58,9 +76,6 @@
     </r>
   </si>
   <si>
-    <t>产品名称</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -69,7 +84,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>主单位</t>
+      <t>副单位</t>
     </r>
     <r>
       <rPr>
@@ -91,7 +106,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>副单位</t>
+      <t>转换系数</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +128,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>转换系数</t>
+      <t>计算方向</t>
     </r>
     <r>
       <rPr>
@@ -135,7 +150,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>计算方向</t>
+      <t>产品来源</t>
     </r>
     <r>
       <rPr>
@@ -149,6 +164,9 @@
     </r>
   </si>
   <si>
+    <t>品牌</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -157,7 +175,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>产品来源</t>
+      <t>型号</t>
     </r>
     <r>
       <rPr>
@@ -171,9 +189,6 @@
     </r>
   </si>
   <si>
-    <t>品牌</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -182,7 +197,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>型号</t>
+      <t>密封盖-结构</t>
     </r>
     <r>
       <rPr>
@@ -196,6 +211,9 @@
     </r>
   </si>
   <si>
+    <t>密封盖-打字</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -204,7 +222,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>密封盖-结构</t>
+      <t>结构类型</t>
     </r>
     <r>
       <rPr>
@@ -218,9 +236,6 @@
     </r>
   </si>
   <si>
-    <t>密封盖-打字</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -229,7 +244,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>结构类型</t>
+      <t>游隙</t>
     </r>
     <r>
       <rPr>
@@ -243,6 +258,9 @@
     </r>
   </si>
   <si>
+    <t>钢球厂家</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -251,7 +269,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>游隙</t>
+      <t>油脂</t>
     </r>
     <r>
       <rPr>
@@ -265,7 +283,7 @@
     </r>
   </si>
   <si>
-    <t>钢球厂家</t>
+    <t>油脂量</t>
   </si>
   <si>
     <r>
@@ -276,7 +294,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>油脂</t>
+      <t>噪音</t>
     </r>
     <r>
       <rPr>
@@ -290,9 +308,6 @@
     </r>
   </si>
   <si>
-    <t>油脂量</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -301,7 +316,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>噪音</t>
+      <t>保持架</t>
     </r>
     <r>
       <rPr>
@@ -315,8 +330,27 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>保持架</t>
+    <t>振动等级</t>
+  </si>
+  <si>
+    <t>精度等级</t>
+  </si>
+  <si>
+    <t>颜色</t>
+  </si>
+  <si>
+    <t>孔径</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否销售</t>
     </r>
     <r>
       <rPr>
@@ -330,20 +364,15 @@
     </r>
   </si>
   <si>
-    <t>振动等级</t>
-  </si>
-  <si>
-    <t>精度等级</t>
-  </si>
-  <si>
-    <t>颜色</t>
-  </si>
-  <si>
-    <t>孔径</t>
-  </si>
-  <si>
-    <r>
-      <t>是否销售</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否贸易件</t>
     </r>
     <r>
       <rPr>
@@ -358,21 +387,13 @@
   </si>
   <si>
     <r>
-      <t>是否贸易件</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(必填)</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>是否生成BOM</t>
     </r>
     <r>
@@ -1675,25 +1696,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AB48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="23.5555555555556" customWidth="1"/>
-    <col min="4" max="4" width="17.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="15.2222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.225" customWidth="1"/>
+    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
+    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.225" customWidth="1"/>
     <col min="6" max="6" width="15.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="17.2222222222222" customWidth="1"/>
-    <col min="8" max="10" width="16.4444444444444" customWidth="1"/>
+    <col min="7" max="7" width="17.225" customWidth="1"/>
+    <col min="8" max="10" width="16.4416666666667" customWidth="1"/>
     <col min="11" max="11" width="14.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="21.7777777777778" customWidth="1"/>
+    <col min="12" max="12" width="21.775" customWidth="1"/>
     <col min="13" max="13" width="14.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="16.7777777777778" customWidth="1"/>
+    <col min="14" max="14" width="16.775" customWidth="1"/>
     <col min="15" max="24" width="14.6666666666667" customWidth="1"/>
-    <col min="25" max="25" width="16.8888888888889" customWidth="1"/>
-    <col min="26" max="26" width="19.4444444444444" customWidth="1"/>
-    <col min="27" max="27" width="21.5555555555556" customWidth="1"/>
-    <col min="28" max="28" width="19.4444444444444" customWidth="1"/>
+    <col min="25" max="25" width="16.8916666666667" customWidth="1"/>
+    <col min="26" max="26" width="19.4416666666667" customWidth="1"/>
+    <col min="27" max="27" width="21.5583333333333" customWidth="1"/>
+    <col min="28" max="28" width="19.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:28">
@@ -1885,9 +1906,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="94.8888888888889" style="1" customWidth="1"/>
+    <col min="1" max="1" width="94.8916666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">

--- a/public/static/成品导入模板.xlsx
+++ b/public/static/成品导入模板.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>序号</t>
   </si>
@@ -37,6 +37,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>品名规格</t>
     </r>
     <r>
@@ -406,6 +413,9 @@
       </rPr>
       <t>(必填)</t>
     </r>
+  </si>
+  <si>
+    <t>工艺路线</t>
   </si>
   <si>
     <t>备注</t>
@@ -1695,7 +1705,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB48"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
@@ -1715,9 +1725,10 @@
     <col min="26" max="26" width="19.4416666666667" customWidth="1"/>
     <col min="27" max="27" width="21.5583333333333" customWidth="1"/>
     <col min="28" max="28" width="19.4416666666667" customWidth="1"/>
+    <col min="29" max="29" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:28">
+    <row r="1" ht="25" customHeight="1" spans="1:29">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1802,10 +1813,13 @@
       <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:28">
+    <row r="2" ht="20" customHeight="1" spans="1:29">
       <c r="A2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1814,10 +1828,10 @@
       <c r="F2" s="5"/>
       <c r="G2" s="4"/>
       <c r="H2" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -1838,6 +1852,7 @@
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1893,7 +1908,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
       <formula1>"组装,生产,采购,外协"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 Z2 AA2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:AA2">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1913,42 +1928,42 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="43" customHeight="1" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1"/>

--- a/public/static/成品导入模板.xlsx
+++ b/public/static/成品导入模板.xlsx
@@ -28,9 +28,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>序号</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>产品分类</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
   </si>
   <si>
     <t>产品编码</t>
@@ -1705,30 +1727,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AD48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18.225" customWidth="1"/>
-    <col min="3" max="3" width="23.5583333333333" customWidth="1"/>
-    <col min="4" max="4" width="17.5583333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.225" customWidth="1"/>
-    <col min="6" max="6" width="15.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="17.225" customWidth="1"/>
-    <col min="8" max="10" width="16.4416666666667" customWidth="1"/>
-    <col min="11" max="11" width="14.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="21.775" customWidth="1"/>
-    <col min="13" max="13" width="14.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="16.775" customWidth="1"/>
-    <col min="15" max="24" width="14.6666666666667" customWidth="1"/>
-    <col min="25" max="25" width="16.8916666666667" customWidth="1"/>
-    <col min="26" max="26" width="19.4416666666667" customWidth="1"/>
-    <col min="27" max="27" width="21.5583333333333" customWidth="1"/>
-    <col min="28" max="28" width="19.4416666666667" customWidth="1"/>
-    <col min="29" max="29" width="19" customWidth="1"/>
+    <col min="2" max="3" width="18.225" customWidth="1"/>
+    <col min="4" max="4" width="23.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="17.5583333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.225" customWidth="1"/>
+    <col min="7" max="7" width="15.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="17.225" customWidth="1"/>
+    <col min="9" max="11" width="16.4416666666667" customWidth="1"/>
+    <col min="12" max="12" width="14.6666666666667" customWidth="1"/>
+    <col min="13" max="13" width="21.775" customWidth="1"/>
+    <col min="14" max="14" width="14.6666666666667" customWidth="1"/>
+    <col min="15" max="15" width="16.775" customWidth="1"/>
+    <col min="16" max="25" width="14.6666666666667" customWidth="1"/>
+    <col min="26" max="26" width="16.8916666666667" customWidth="1"/>
+    <col min="27" max="27" width="19.4416666666667" customWidth="1"/>
+    <col min="28" max="28" width="21.5583333333333" customWidth="1"/>
+    <col min="29" max="29" width="19.4416666666667" customWidth="1"/>
+    <col min="30" max="30" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:29">
+    <row r="1" ht="25" customHeight="1" spans="1:30">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1810,30 +1832,33 @@
       <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:29">
+    <row r="2" ht="20" customHeight="1" spans="1:30">
       <c r="A2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="7" t="s">
-        <v>30</v>
-      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="7"/>
+      <c r="J2" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
       <c r="M2" s="7"/>
@@ -1849,10 +1874,11 @@
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
-      <c r="Z2" s="4"/>
+      <c r="Z2" s="7"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
     </row>
     <row r="3" ht="20" customHeight="1"/>
     <row r="4" ht="20" customHeight="1"/>
@@ -1902,13 +1928,13 @@
     <row r="48" ht="20" customHeight="1"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
       <formula1>"乘,除"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2">
       <formula1>"组装,生产,采购,外协"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:AA2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:AB2">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1928,42 +1954,42 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="43" customHeight="1" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1"/>

--- a/public/static/成品导入模板.xlsx
+++ b/public/static/成品导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="成品导入模板" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>序号</t>
   </si>
@@ -474,6 +474,12 @@
   </si>
   <si>
     <t>如果是贸易件时，密封盖-结构、密封盖-打字、结构类型、游隙、钢球厂家、油脂、油脂量、噪音、保持架、振动等级、精度等级、颜色、孔径等都非必填，然后产品来源固定死采购</t>
+  </si>
+  <si>
+    <t>产品分类：填写产品分类编码</t>
+  </si>
+  <si>
+    <t>工艺路线：填写工艺路线编码</t>
   </si>
 </sst>
 </file>
@@ -1992,8 +1998,16 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1"/>
-    <row r="10" ht="28" customHeight="1"/>
+    <row r="9" ht="28" customHeight="1" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="11" ht="28" customHeight="1"/>
     <row r="12" ht="28" customHeight="1"/>
     <row r="13" ht="28" customHeight="1"/>
